--- a/public/records.xlsx
+++ b/public/records.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Все" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Женщины, бассейн 50 м" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Женщины, бассейн 25 м" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мужчины, бассейн 50 м" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мужчины, бассейн 25 м" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Смешанные эстафеты" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Все" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Женщины, бассейн 50 м" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Женщины, бассейн 25 м" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Мужчины, бассейн 50 м" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Мужчины, бассейн 25 м" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Смешанные эстафеты" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,10 +32,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00FAFAFA"/>
     </font>
     <font>
-      <name val="Menlo"/>
+      <name val="Consolas"/>
     </font>
   </fonts>
   <fills count="3">
@@ -47,7 +47,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000369A1"/>
+        <fgColor rgb="000D0D0D"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,7 +68,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -523,12 +525,12 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>27.51</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>27.51</t>
         </is>
@@ -571,12 +573,12 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>30.40</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>30.40</t>
         </is>
@@ -619,12 +621,12 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>25.79</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>25.79</t>
         </is>
@@ -667,12 +669,12 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>24.87</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>24.87</t>
         </is>
@@ -715,12 +717,12 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>59.46</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>59.46</t>
         </is>
@@ -763,12 +765,12 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1:05.90</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>65.90</t>
         </is>
@@ -811,12 +813,12 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>57.96</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>57.96</t>
         </is>
@@ -855,33 +857,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Клепикова Дарья</t>
+          <t>Манохина Кира</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>54.45</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>54.45</t>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>54.07</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>54.07</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.04.2022</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -893,7 +895,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м</t>
+          <t>на спине 200 м</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -903,33 +905,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Опёнышева Арина</t>
+          <t>Устинова Дарья К.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>54.45</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>54.45</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2:08.02</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>128.02</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>24.06.2015</t>
+          <t>14.05.2014</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2015-06-24</t>
+          <t>2014-05-14</t>
         </is>
       </c>
     </row>
@@ -941,7 +943,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>на спине 200 м</t>
+          <t>брасс 200 м</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -951,33 +953,33 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Устинова Дарья К.</t>
+          <t>Чикунова Евгения</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2:08.02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>128.02</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2:20.57</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>140.57</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Токио</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>14.05.2014</t>
+          <t>29.07.2021</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
+          <t>2021-07-29</t>
         </is>
       </c>
     </row>
@@ -989,7 +991,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>брасс 200 м</t>
+          <t>баттерфляй 200 м</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -999,33 +1001,33 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Чикунова Евгения</t>
+          <t>Фокина Серафима</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2:20.57</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>140.57</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2:07.67</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>127.67</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Токио</t>
+          <t>Отопени</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>29.07.2021</t>
+          <t>20.08.2025</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2021-07-29</t>
+          <t>2025-08-20</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1039,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м</t>
+          <t>вольный стиль 200 м</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1047,33 +1049,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Фокина Серафима</t>
+          <t>Мишарина Ксения</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2:07.67</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>127.67</t>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1:58.06</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>118.06</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>19.04.2026</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2026-04-19</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1087,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м</t>
+          <t>комплексное плавание 200 м</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1095,33 +1097,33 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Баклакова Мария</t>
+          <t>Блинова Виктория</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1:58.21</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>118.21</t>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2:12.60</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>132.60</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Познань</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.07.2013</t>
+          <t>20.04.2026</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2013-07-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1135,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м</t>
+          <t>вольный стиль 400 м</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1143,33 +1145,33 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Сорокина Анастасия</t>
+          <t>Дьякова Софья</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2:12.90</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>132.90</t>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4:05.16</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>245.16</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>05.04.2021</t>
+          <t>26.07.2024</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2021-04-05</t>
+          <t>2024-07-26</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1183,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м</t>
+          <t>комплексное плавание 400 м</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1191,33 +1193,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Дьякова Софья</t>
+          <t>Блинова Виктория</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>4:05.16</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>245.16</t>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4:38.48</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>278.48</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>26.07.2024</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1231,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м</t>
+          <t>вольный стиль 800 м</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1239,18 +1241,18 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Сорокина Анастасия</t>
+          <t>Дьякова Софья</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>4:43.44</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>283.44</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8:24.93</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>504.93</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1260,12 +1262,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>03.04.2021</t>
+          <t>14.04.2025</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
+          <t>2025-04-14</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1279,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м</t>
+          <t>вольный стиль 1500 м</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1287,33 +1289,33 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Дьякова Софья</t>
+          <t>Мишарина Ксения</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>8:24.93</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>504.93</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>16:03.42</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>963.42</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14.04.2025</t>
+          <t>17.04.2026</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
     </row>
@@ -1325,43 +1327,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м</t>
+          <t>4 х 100 м вольный стиль</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>личное</t>
+          <t>эстафета</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Мишарина Ксения</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>16:04.21</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>964.21</t>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Манохина Кира · Полещук Мария · Захарова Алиса · Степанова Милана</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3:37.87</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>217.87</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Отопени</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>23.08.2025</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-08-23</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1379,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>4 х 100 м комбинированная</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1388,32 +1394,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Манохина Кира · Полещук Мария · Захарова Алиса · Степанова Милана</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>3:37.87</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>217.87</t>
+          <t>Васькина Дарья · Чикунова Евгения · Сабитова Александра · Никонова Екатерина</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4:00.30</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>240.30</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>23.08.2025</t>
+          <t>25.08.2019</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2019-08-25</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1431,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная</t>
+          <t>4 х 200 м вольный стиль</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1440,84 +1446,80 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Васькина Дарья · Чикунова Евгения · Сабитова Александра · Никонова Екатерина</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>4:00.30</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>240.30</t>
+          <t>Мишарина Ксения · Дьякова Софья · Брыканова Арина · Сорокина Ксения</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>7:57.34</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>477.34</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25.08.2019</t>
+          <t>09.07.2026</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2019-08-25</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Женщины, бассейн 50 м</t>
+          <t>Женщины, бассейн 25 м</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль</t>
+          <t>на спине 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>эстафета</t>
+          <t>личное</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Дьякова Софья · Мишарина Ксения · Колпакова Анастасия · Степанова Милана</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>7:59.62</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>479.62</t>
+          <t>Осетрова Мария</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>26.33</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>26.33</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>19.08.2025</t>
+          <t>20.12.2024</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1531,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>на спине 50 м (бассейн 25 м)</t>
+          <t>брасс 50 м  (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1539,33 +1541,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Осетрова Мария</t>
+          <t>Гилязова Ралина</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>26.33</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>26.33</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>29.62</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>29.62</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20.12.2024</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-11-12</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1579,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>брасс 50 м  (бассейн 25 м)</t>
+          <t>баттерфляй 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1587,33 +1589,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Гилязова Ралина</t>
+          <t>Осетрова Мария</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>29.62</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>29.62</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>25.66</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>25.66</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Минск</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>22.11.2025</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-22</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1627,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м (бассейн 25 м)</t>
+          <t>вольный стиль 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1635,33 +1637,33 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Осетрова Мария</t>
+          <t>Насретдинова Розалия</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>25.66</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>25.66</t>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>24.15</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>24.15</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Минск</t>
+          <t>Хернинг</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>22.11.2025</t>
+          <t>15.12.2013</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2013-12-15</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1675,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м (бассейн 25 м)</t>
+          <t>на спине 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1683,33 +1685,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Насретдинова Розалия</t>
+          <t>Степанова Милана</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>24.15</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>24.15</t>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>57.26</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>57.26</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Хернинг</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15.12.2013</t>
+          <t>23.11.2025</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2013-12-15</t>
+          <t>2025-11-23</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1723,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>на спине 100 м (бассейн 25 м)</t>
+          <t>брасс 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1731,33 +1733,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Степанова Милана</t>
+          <t>Чикунова Евгения</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>57.26</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>57.26</t>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1:04.25</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>64.25</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23.11.2025</t>
+          <t>03.11.2021</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2021-11-03</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1771,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>брасс 100 м (бассейн 25 м)</t>
+          <t>баттерфляй 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1779,33 +1781,33 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Чикунова Евгения</t>
+          <t>Сабитова Александра</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>1:04.25</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>64.25</t>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>56.84</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>56.84</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>03.11.2021</t>
+          <t>22.12.2017</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2021-11-03</t>
+          <t>2017-12-22</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1819,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м (бассейн 25 м)</t>
+          <t>вольный стиль 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1827,18 +1829,18 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Сабитова Александра</t>
+          <t>Кузнецова Александра</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>56.84</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>56.84</t>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>52.86</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>52.86</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1848,12 +1850,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>22.12.2017</t>
+          <t>20.12.2024</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2017-12-22</t>
+          <t>2024-12-20</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1867,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м (бассейн 25 м)</t>
+          <t>комплексное плавание 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1875,33 +1877,33 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Кузнецова Александра</t>
+          <t>Гилязова Ралина</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>52.86</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>52.86</t>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>59.20</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>59.20</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20.12.2024</t>
+          <t>10.11.2025</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-11-10</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1915,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>комплексное плавание 100 м (бассейн 25 м)</t>
+          <t>на спине 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1923,33 +1925,33 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Гилязова Ралина</t>
+          <t>Степанова Милана</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>59.20</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>59.20</t>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2:03.84</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>123.84</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10.11.2025</t>
+          <t>19.12.2025</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-12-19</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1963,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>на спине 200 м (бассейн 25 м)</t>
+          <t>брасс 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1971,33 +1973,33 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Степанова Милана</t>
+          <t>Чикунова Евгения</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2:03.84</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>123.84</t>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2:16.88</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>136.88</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>19.12.2025</t>
+          <t>05.11.2021</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2021-11-05</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2011,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>брасс 200 м (бассейн 25 м)</t>
+          <t>баттерфляй 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2019,33 +2021,33 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Чикунова Евгения</t>
+          <t>Маркова Анастасия</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2:16.88</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>136.88</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2:05.97</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>125.97</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Абу Даби</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>05.11.2021</t>
+          <t>17.12.2021</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2021-11-05</t>
+          <t>2021-12-17</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2059,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м (бассейн 25 м)</t>
+          <t>вольный стиль 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2067,33 +2069,33 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Маркова Анастасия</t>
+          <t>Степанова Милана</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2:05.97</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>125.97</t>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1:54.37</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>114.37</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Абу Даби</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>17.12.2021</t>
+          <t>09.11.2025</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2021-12-17</t>
+          <t>2025-11-09</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2107,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м (бассейн 25 м)</t>
+          <t>комплексное плавание 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2115,33 +2117,33 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Степанова Милана</t>
+          <t>Сорокина Анастасия</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1:54.37</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>114.37</t>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2:09.38</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>129.38</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>09.11.2025</t>
+          <t>20.11.2021</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2021-11-20</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2155,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м (бассейн 25 м)</t>
+          <t>вольный стиль 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2163,18 +2165,18 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Сорокина Анастасия</t>
+          <t>Дьякова Софья</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2:09.38</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>129.38</t>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>4:01.16</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>241.16</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2184,12 +2186,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20.11.2021</t>
+          <t>20.12.2024</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
+          <t>2024-12-20</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2203,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м (бассейн 25 м)</t>
+          <t>комплексное плавание 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2211,18 +2213,18 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Дьякова Софья</t>
+          <t>Сорокина Анастасия</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>4:01.16</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>241.16</t>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>4:31.29</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>271.29</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2232,12 +2234,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20.12.2024</t>
+          <t>16.11.2021</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2021-11-16</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2251,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м (бассейн 25 м)</t>
+          <t>вольный стиль 800 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2259,18 +2261,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Сорокина Анастасия</t>
+          <t>Мишарина Ксения</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>4:31.29</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>271.29</t>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>8:15.85</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>495.85</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2280,12 +2282,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16.11.2021</t>
+          <t>16.12.2023</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2023-12-16</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2299,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м (бассейн 25 м)</t>
+          <t>вольный стиль 1500 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2311,29 +2313,29 @@
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>8:15.85</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>495.85</t>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>15:42.14</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>942.14</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16.12.2023</t>
+          <t>10.11.2025</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2023-12-16</t>
+          <t>2025-11-10</t>
         </is>
       </c>
     </row>
@@ -2345,43 +2347,47 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м (бассейн 25 м)</t>
+          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>личное</t>
+          <t>эстафета</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Мишарина Ксения</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>15:42.14</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>942.14</t>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Захарова Алиса · Малаева Василиса · Кирейцева Анна · Полещук Мария</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1:38.70</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>98.70</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Саранск</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10.11.2025</t>
+          <t>29.11.2024</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-11-29</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2399,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2408,17 +2414,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Захарова Алиса · Малаева Василиса · Кирейцева Анна · Полещук Мария</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1:38.70</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>98.70</t>
+          <t>Колобродова Александра · Едапина Арина · Хвесюк Варвара · Полещук Мария</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1:48.91</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>108.91</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2428,12 +2434,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>29.11.2024</t>
+          <t>07.12.2025</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2025-12-07</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2451,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2455,37 +2461,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Московская область</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Колобродова Александра · Едапина Арина · Хвесюк Варвара · Полещук Мария</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1:48.91</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>108.91</t>
+          <t>Мельникова Елизавета · Чернышева Анна · Турчина Ольга · Макарова Анастасия Р.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>3:45.34</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>225.34</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Саранск</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>07.12.2025</t>
+          <t>05.11.2019</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2019-11-05</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2503,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2507,22 +2513,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Московская область</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Мельникова Елизавета · Чернышева Анна · Турчина Ольга · Макарова Анастасия Р.</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>3:45.34</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>225.34</t>
+          <t>Колобродова Александра · Едапина Арина · Хвесюк Варвара · Полещук Мария</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>3:57.50</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>237.50</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2532,12 +2538,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>05.11.2019</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
+          <t>2025-11-12</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2555,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2559,22 +2565,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Московская область</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Колобродова Александра · Едапина Арина · Хвесюк Варвара · Полещук Мария</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>3:57.50</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>237.50</t>
+          <t>Булычева Мира · Валиуллина Диана · Дерезина Виктория · Лейкина Полина</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>8:08.41</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>488.41</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2584,64 +2590,60 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>09.11.2025</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-09</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Женщины, бассейн 25 м</t>
+          <t>Мужчины, бассейн 50 м</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
+          <t>на спине 50 м</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>эстафета</t>
+          <t>личное</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Московская область</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Булычева Мира · Валиуллина Диана · Дерезина Виктория · Лейкина Полина</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>8:08.41</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>488.41</t>
+          <t>Колесников Климент</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>24.00</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>24.00</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Глазго</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>09.11.2025</t>
+          <t>04.08.2018</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2018-08-04</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2655,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>на спине 50 м</t>
+          <t>брасс 50 м</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2663,33 +2665,33 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
+          <t>Троценко Максим</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>24.00</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>24.00</t>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>27.15</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>27.15</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Глазго</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>04.08.2018</t>
+          <t>23.07.2022</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2018-08-04</t>
+          <t>2022-07-23</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2703,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>брасс 50 м</t>
+          <t>баттерфляй 50 м</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2711,18 +2713,18 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Троценко Максим</t>
+          <t>Минаков Андрей</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>27.15</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>27.15</t>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>23.05</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>23.05</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2732,12 +2734,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>23.07.2022</t>
+          <t>28.10.2020</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2022-07-23</t>
+          <t>2020-10-28</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2751,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м</t>
+          <t>вольный стиль 50 м</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2759,33 +2761,33 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Минаков Андрей</t>
+          <t>Седов Евгений</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>23.05</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>23.05</t>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>22.06</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>22.06</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Познань</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>28.10.2020</t>
+          <t>14.07.2013</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2020-10-28</t>
+          <t>2013-07-14</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2799,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м</t>
+          <t>на спине 100 м</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2807,33 +2809,33 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Седов Евгений</t>
+          <t>Лифинцев Мирон</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>22.06</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>22.06</t>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>52.08</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>52.08</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Познань</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>14.07.2013</t>
+          <t>28.07.2024</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2013-07-14</t>
+          <t>2024-07-28</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2847,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>на спине 100 м</t>
+          <t>брасс 100 м</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2855,33 +2857,33 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Лифинцев Мирон</t>
+          <t>Герасименко Владислав</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>52.08</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>52.08</t>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>59.97</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>59.97</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>28.07.2024</t>
+          <t>21.08.2019</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2019-08-21</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2895,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>брасс 100 м</t>
+          <t>баттерфляй 100 м</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2903,33 +2905,33 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Герасименко Владислав</t>
+          <t>Минаков Андрей</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>59.97</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>59.97</t>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>50.83</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>50.83</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Кванджу</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>21.08.2019</t>
+          <t>27.07.2019</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2019-08-21</t>
+          <t>2019-07-27</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2943,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м</t>
+          <t>вольный стиль 100 м</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2955,29 +2957,29 @@
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>50.83</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>50.83</t>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>47.57</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>47.57</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Кванджу</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>27.07.2019</t>
+          <t>30.10.2020</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2019-07-27</t>
+          <t>2020-10-30</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2991,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м</t>
+          <t>на спине 200 м</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2999,33 +3001,33 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Минаков Андрей</t>
+          <t>Колесников Климент</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>47.57</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>47.57</t>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1:55.14</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>115.14</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>30.10.2020</t>
+          <t>28.07.2017</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2020-10-30</t>
+          <t>2017-07-28</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3039,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>на спине 200 м</t>
+          <t>брасс 200 м</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3047,33 +3049,33 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
+          <t>Чупков Антон</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1:55.14</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>115.14</t>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2:09.64</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>129.64</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>28.07.2017</t>
+          <t>06.08.2015</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2017-07-28</t>
+          <t>2015-08-06</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3087,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>брасс 200 м</t>
+          <t>баттерфляй 200 м</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3095,18 +3097,18 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Чупков Антон</t>
+          <t>Клименищев Вадим</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2:09.64</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>129.64</t>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1:56.50</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>116.50</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3116,12 +3118,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>06.08.2015</t>
+          <t>30.10.2020</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2015-08-06</t>
+          <t>2020-10-30</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3135,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м</t>
+          <t>вольный стиль 200 м</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3143,33 +3145,33 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Клименищев Вадим</t>
+          <t>Изотов Данила</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1:56.50</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>116.50</t>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1:43.90</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>103.90</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Рим</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>30.10.2020</t>
+          <t>28.07.2009</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2020-10-30</t>
+          <t>2009-07-28</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3183,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м</t>
+          <t>комплексное плавание 200 м</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3191,33 +3193,33 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Изотов Данила</t>
+          <t>Щербаков Михаил</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1:43.90</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>103.90</t>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1:57.07</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>117.07</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Рим</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>28.07.2009</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3231,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м</t>
+          <t>вольный стиль 400 м</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3239,33 +3241,33 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Щербаков Михаил</t>
+          <t>Вековищев Григорий</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1:57.25</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>117.25</t>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>3:44.58</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>224.58</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>12.07.2026</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3279,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м</t>
+          <t>комплексное плавание 400 м</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3287,33 +3289,33 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Вековищев Григорий</t>
+          <t>Бородин Илья</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>3:46.64</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>226.64</t>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>4:10.02</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>250.02</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>19.08.2025</t>
+          <t>23.05.2021</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2021-05-23</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3327,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м</t>
+          <t>вольный стиль 800 м</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3335,18 +3337,18 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Бородин Илья</t>
+          <t>Сибирцев Илья</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>4:10.02</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>250.02</t>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>7:48.05</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>468.05</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3356,12 +3358,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>23.05.2021</t>
+          <t>22.08.2019</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2019-08-22</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3375,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м</t>
+          <t>вольный стиль 1500 м</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3383,33 +3385,33 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Сибирцев Илья</t>
+          <t>Дружинин Илья</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>7:48.05</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>468.05</t>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>14:59.56</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>899.56</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Рио-де-Жанейро</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>22.08.2019</t>
+          <t>12.08.2016</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2019-08-22</t>
+          <t>2016-08-12</t>
         </is>
       </c>
     </row>
@@ -3421,43 +3423,47 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м</t>
+          <t>4 х 100 м вольный стиль</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>личное</t>
+          <t>эстафета</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Дружинин Илья</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>14:59.56</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>899.56</t>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Торопкин Богдан · Прошин Егор · Миляев Матвей · Щербаков Михаил</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>3:12.75</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>192.75</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Рио-де-Жанейро</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>12.08.2016</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2016-08-12</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3475,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>4 х 100 м комбинированная</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3484,32 +3490,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Щербаков Михаил · Жидков Роман · Прошин Егор · Злотников Георгий</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>3:15.38</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>195.38</t>
+          <t>Зуев Николай · Герасименко Владислав · Минаков Андрей · Щёголев Александр</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>3:33.19</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>213.19</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>19.08.2025</t>
+          <t>25.08.2019</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2019-08-25</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3527,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная</t>
+          <t>4 х 200 м вольный стиль</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3536,84 +3542,80 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Зуев Николай · Герасименко Владислав · Минаков Андрей · Щёголев Александр</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>3:33.19</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>213.19</t>
+          <t>Торопкин Богдан · Щербаков Михаил · Вишняков Савелий · Вековищев Григорий</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>7:09.16</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>429.16</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>25.08.2019</t>
+          <t>11.07.2026</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2019-08-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Мужчины, бассейн 50 м</t>
+          <t>Мужчины, бассейн 25 м</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль</t>
+          <t>на спине 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>эстафета</t>
+          <t>личное</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Щербаков Михаил · Вековищев Григорий · Бабинич Егор · Черепков Андрей</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>7:10.39</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>430.39</t>
+          <t>Лифинцев Мирон</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>22.47</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>22.47</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>22.08.2025</t>
+          <t>13.12.2024</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2024-12-13</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3627,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>на спине 50 м (бассейн 25 м)</t>
+          <t>брасс 50 м  (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3635,33 +3637,33 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Лифинцев Мирон</t>
+          <t>Троценко Максим</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>22.47</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>22.47</t>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>26.24</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>26.24</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>13.12.2024</t>
+          <t>25.11.2022</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2022-11-25</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3675,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>брасс 50 м  (бассейн 25 м)</t>
+          <t>баттерфляй 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3683,33 +3685,33 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Троценко Максим</t>
+          <t>Минаков Андрей</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>26.24</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>26.24</t>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>22.34</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>22.34</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>25.11.2022</t>
+          <t>18.12.2020</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2022-11-25</t>
+          <t>2020-12-18</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3723,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>баттерфляй 50 м (бассейн 25 м)</t>
+          <t>вольный стиль 50 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3731,33 +3733,33 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Минаков Андрей</t>
+          <t>Седов Евгений</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>22.34</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>22.34</t>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>20.70</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>20.70</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Доха</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>18.12.2020</t>
+          <t>06.12.2014</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2020-12-18</t>
+          <t>2014-12-06</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3771,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>вольный стиль 50 м (бассейн 25 м)</t>
+          <t>на спине 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3779,33 +3781,33 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Седов Евгений</t>
+          <t>Лифинцев Мирон</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>20.70</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>20.70</t>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>48.76</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>48.76</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Доха</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>06.12.2014</t>
+          <t>11.12.2024</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2014-12-06</t>
+          <t>2024-12-11</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3819,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>на спине 100 м (бассейн 25 м)</t>
+          <t>брасс 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3827,33 +3829,33 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Лифинцев Мирон</t>
+          <t>Чупков Антон</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>48.76</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>48.76</t>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>57.61</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>57.61</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>11.12.2024</t>
+          <t>09.11.2015</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2015-11-09</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3867,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>брасс 100 м (бассейн 25 м)</t>
+          <t>баттерфляй 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3875,33 +3877,33 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Чупков Антон</t>
+          <t>Минаков Андрей</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>57.61</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>57.61</t>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>50.12</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>50.12</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>09.11.2015</t>
+          <t>22.12.2020</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2015-11-09</t>
+          <t>2020-12-22</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3915,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>баттерфляй 100 м (бассейн 25 м)</t>
+          <t>вольный стиль 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3923,18 +3925,18 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Минаков Андрей</t>
+          <t>Колесников Климент</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>50.12</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>50.12</t>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>46.11</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>46.11</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3944,12 +3946,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>22.12.2020</t>
+          <t>21.12.2018</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
+          <t>2018-12-21</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3963,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м (бассейн 25 м)</t>
+          <t>комплексное плавание 100 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3975,29 +3977,29 @@
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>46.11</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>46.11</t>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>50.63</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>50.63</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Ханчжоу</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>21.12.2018</t>
+          <t>14.12.2018</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2018-12-21</t>
+          <t>2018-12-14</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4011,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>комплексное плавание 100 м (бассейн 25 м)</t>
+          <t>на спине 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4023,29 +4025,29 @@
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>50.63</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>50.63</t>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1:48.02</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>108.02</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Ханчжоу</t>
+          <t>Копенгаген</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>14.12.2018</t>
+          <t>22.11.2017</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2018-12-14</t>
+          <t>2017-11-22</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4059,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>на спине 200 м (бассейн 25 м)</t>
+          <t>брасс 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4067,33 +4069,33 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
+          <t>Чупков Антон</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>1:48.02</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>108.02</t>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2:03.57</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>123.57</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Копенгаген</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>22.11.2017</t>
+          <t>10.11.2015</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2017-11-22</t>
+          <t>2015-11-10</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4107,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>брасс 200 м (бассейн 25 м)</t>
+          <t>баттерфляй 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4115,18 +4117,18 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Чупков Антон</t>
+          <t>Пахомов Даниил</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2:03.57</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>123.57</t>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>1:53.10</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>113.10</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4136,12 +4138,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10.11.2015</t>
+          <t>12.11.2015</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2015-11-10</t>
+          <t>2015-11-12</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4155,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м (бассейн 25 м)</t>
+          <t>вольный стиль 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4163,33 +4165,33 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Пахомов Даниил</t>
+          <t>Колесников Климент</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1:53.10</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>113.10</t>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>1:41.75</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>101.75</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>12.11.2015</t>
+          <t>23.12.2017</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2015-11-12</t>
+          <t>2017-12-23</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4203,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м (бассейн 25 м)</t>
+          <t>комплексное плавание 200 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4211,18 +4213,18 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Колесников Климент</t>
+          <t>Щербаков Михаил</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>1:41.75</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>101.75</t>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>1:52.21</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>112.21</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4232,12 +4234,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>23.12.2017</t>
+          <t>20.12.2025</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2017-12-23</t>
+          <t>2025-12-20</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4251,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м (бассейн 25 м)</t>
+          <t>вольный стиль 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4259,33 +4261,33 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Щербаков Михаил</t>
+          <t>Вековищев Григорий</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1:52.21</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>112.21</t>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>3:36.57</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>216.57</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>20.12.2025</t>
+          <t>09.11.2025</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-11-09</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4299,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м (бассейн 25 м)</t>
+          <t>комплексное плавание 400 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4307,33 +4309,33 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Вековищев Григорий</t>
+          <t>Бородин Илья</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>3:36.57</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>216.57</t>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>3:56.47</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>236.47</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Абу Даби</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>09.11.2025</t>
+          <t>20.12.2021</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2021-12-20</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4347,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м (бассейн 25 м)</t>
+          <t>вольный стиль 800 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4355,33 +4357,33 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Бородин Илья</t>
+          <t>Бабинич Егор</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>3:56.47</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>236.47</t>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>7:39.26</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>459.26</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Абу Даби</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>20.12.2021</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2025-11-11</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4395,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м (бассейн 25 м)</t>
+          <t>вольный стиль 1500 м (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4403,33 +4405,33 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Бабинич Егор</t>
+          <t>Мартынычев Кирилл</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>7:39.26</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>459.26</t>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>14:30.17</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>870.17</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>19.12.2020</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2020-12-19</t>
         </is>
       </c>
     </row>
@@ -4441,28 +4443,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м (бассейн 25 м)</t>
+          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>личное</t>
+          <t>эстафета</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Мартынычев Кирилл</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>14:30.17</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>870.17</t>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Назаренко Александр · Жидков Роман · Зуев Вячеслав · Захариков Илья</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>1:26.37</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>86.37</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4472,12 +4478,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>19.12.2020</t>
+          <t>20.12.2024</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2020-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4495,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4504,17 +4510,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Назаренко Александр · Жидков Роман · Зуев Вячеслав · Захариков Илья</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>1:26.37</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>86.37</t>
+          <t>Прошин Егор · Тимофеев Глеб · Жидков Роман · Захариков Илья</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>1:34.99</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>94.99</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4524,12 +4530,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>20.12.2024</t>
+          <t>21.12.2024</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-12-21</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4547,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4551,37 +4557,37 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Сборная России</t>
+          <t>Воронежская область</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Прошин Егор · Тимофеев Глеб · Жидков Роман · Захариков Илья</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>1:34.99</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>94.99</t>
+          <t>Котляренко Артем · Кривенченко Виталий · Кравцов Дмитрий · Рахманин Никита</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>3:20.97</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>200.97</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>21.12.2024</t>
+          <t>07.11.2025</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2025-11-07</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4599,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4608,17 +4614,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Котляренко Артем · Кривенченко Виталий · Кравцов Дмитрий · Рахманин Никита</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>3:20.97</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>200.97</t>
+          <t>Котляренко Артём · Кривенченко Виталий · Теньков Арсений · Рахманин Никита</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>3:38.45</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>218.45</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4628,12 +4634,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>07.11.2025</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-12</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4651,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4655,22 +4661,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Воронежская область</t>
+          <t>Нижегородская область</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Котляренко Артём · Кривенченко Виталий · Теньков Арсений · Рахманин Никита</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>3:38.45</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>218.45</t>
+          <t>Лозе Ярослав · Васильев Петр · Журов Данила · Власов Алексей</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>7:10.29</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>430.29</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4680,24 +4686,24 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>10.11.2025</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-10</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Мужчины, бассейн 25 м</t>
+          <t>Смешанные эстафеты</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>4 х 200 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4707,37 +4713,37 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Нижегородская область</t>
+          <t>Сборная России</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Лозе Ярослав · Васильев Петр · Журов Данила · Власов Алексей</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>7:10.29</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>430.29</t>
+          <t>Курганский Павел · Мальцев Антон · Кузнецова Александра · Полещук Мария</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1:32.10</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>92.10</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Саранск</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>10.11.2025</t>
+          <t>01.12.2023</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2023-12-01</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4755,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4 х 50 м вольный стиль (бассейн 25 м)</t>
+          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4759,22 +4765,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Сборная России</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Курганский Павел · Мальцев Антон · Кузнецова Александра · Полещук Мария</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1:32.10</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>92.10</t>
+          <t>Колобродова Александра · Писецкий Даниил · Прошин Егор · Полещук Мария</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>1:41.23</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>101.23</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4784,12 +4790,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>01.12.2023</t>
+          <t>08.12.2025</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4807,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4 х 50 м комбинированная (бассейн 25 м)</t>
+          <t>4 х 100 м вольный стиль</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4811,37 +4817,37 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Сборная России</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Колобродова Александра · Писецкий Даниил · Прошин Егор · Полещук Мария</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>1:41.23</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>101.23</t>
+          <t>Прошин Егор · Щербаков Михаил · Сорокина Ксения · Манохина Кира</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>3:23.96</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>203.96</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Саранск</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>08.12.2025</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4859,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>4 х 100 м комбинированная</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4868,17 +4874,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Щербаков Михаил · Жидков Роман · Полещук Мария · Манохина Кира</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>3:26.93</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>206.93</t>
+          <t>Яковлев Георгий · Плотников Олег · Фокина Серафима · Манохина Кира</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>3:46.48</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>226.48</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4888,62 +4894,10 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>21.08.2025</t>
+          <t>20.08.2025</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Смешанные эстафеты</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>4 х 100 м комбинированная</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>эстафета</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Яковлев Георгий · Плотников Олег · Фокина Серафима · Манохина Кира</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>3:46.48</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>226.48</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Отопени</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>20.08.2025</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
         <is>
           <t>2025-08-20</t>
         </is>
@@ -4960,7 +4914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5207,237 +5161,237 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Клепикова Дарья</t>
+          <t>Манохина Кира</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54.45</t>
+          <t>54.07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>26.04.2022</t>
+          <t>10.07.2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>вольный стиль 100 м</t>
+          <t>на спине 200 м</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Опёнышева Арина</t>
+          <t>Устинова Дарья К.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>54.45</t>
+          <t>2:08.02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.06.2015</t>
+          <t>14.05.2014</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>на спине 200 м</t>
+          <t>брасс 200 м</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Устинова Дарья К.</t>
+          <t>Чикунова Евгения</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2:08.02</t>
+          <t>2:20.57</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Токио</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14.05.2014</t>
+          <t>29.07.2021</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>брасс 200 м</t>
+          <t>баттерфляй 200 м</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Чикунова Евгения</t>
+          <t>Фокина Серафима</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2:20.57</t>
+          <t>2:07.67</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Токио</t>
+          <t>Отопени</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.07.2021</t>
+          <t>20.08.2025</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>баттерфляй 200 м</t>
+          <t>вольный стиль 200 м</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Фокина Серафима</t>
+          <t>Мишарина Ксения</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2:07.67</t>
+          <t>1:58.06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>19.04.2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>вольный стиль 200 м</t>
+          <t>комплексное плавание 200 м</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Баклакова Мария</t>
+          <t>Блинова Виктория</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1:58.21</t>
+          <t>2:12.60</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Познань</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.07.2013</t>
+          <t>20.04.2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>комплексное плавание 200 м</t>
+          <t>вольный стиль 400 м</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Сорокина Анастасия</t>
+          <t>Дьякова Софья</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2:12.90</t>
+          <t>4:05.16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>05.04.2021</t>
+          <t>26.07.2024</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>вольный стиль 400 м</t>
+          <t>комплексное плавание 400 м</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Дьякова Софья</t>
+          <t>Блинова Виктория</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4:05.16</t>
+          <t>4:38.48</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>26.07.2024</t>
+          <t>21.04.2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>комплексное плавание 400 м</t>
+          <t>вольный стиль 800 м</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Сорокина Анастасия</t>
+          <t>Дьякова Софья</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4:43.44</t>
+          <t>8:24.93</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5447,70 +5401,74 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>03.04.2021</t>
+          <t>14.04.2025</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>вольный стиль 800 м</t>
+          <t>вольный стиль 1500 м</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Дьякова Софья</t>
+          <t>Мишарина Ксения</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8:24.93</t>
+          <t>16:03.42</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.04.2025</t>
+          <t>17.04.2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>вольный стиль 1500 м</t>
+          <t>4 х 100 м вольный стиль</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Мишарина Ксения</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>Сборная России</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Манохина Кира · Полещук Мария · Захарова Алиса · Степанова Милана</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16:04.21</t>
+          <t>3:37.87</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Отопени</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17.04.2025</t>
+          <t>23.08.2025</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4 х 100 м вольный стиль</t>
+          <t>4 х 100 м комбинированная</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5520,29 +5478,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Манохина Кира · Полещук Мария · Захарова Алиса · Степанова Милана</t>
+          <t>Васькина Дарья · Чикунова Евгения · Сабитова Александра · Никонова Екатерина</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3:37.87</t>
+          <t>4:00.30</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Будапешт</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>23.08.2025</t>
+          <t>25.08.2019</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4 х 100 м комбинированная</t>
+          <t>4 х 200 м вольный стиль</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5552,54 +5510,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Васькина Дарья · Чикунова Евгения · Сабитова Александра · Никонова Екатерина</t>
+          <t>Мишарина Ксения · Дьякова Софья · Брыканова Арина · Сорокина Ксения</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4:00.30</t>
+          <t>7:57.34</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Будапешт</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25.08.2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>4 х 200 м вольный стиль</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Сборная России</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Дьякова Софья · Мишарина Ксения · Колпакова Анастасия · Степанова Милана</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>7:59.62</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Отопени</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>19.08.2025</t>
+          <t>09.07.2026</t>
         </is>
       </c>
     </row>
@@ -6725,17 +6651,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1:57.25</t>
+          <t>1:57.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>08.07.2026</t>
         </is>
       </c>
     </row>
@@ -6753,17 +6679,17 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3:46.64</t>
+          <t>3:44.58</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>19.08.2025</t>
+          <t>12.07.2026</t>
         </is>
       </c>
     </row>
@@ -6864,22 +6790,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Щербаков Михаил · Жидков Роман · Прошин Егор · Злотников Георгий</t>
+          <t>Торопкин Богдан · Прошин Егор · Миляев Матвей · Щербаков Михаил</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3:15.38</t>
+          <t>3:12.75</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19.08.2025</t>
+          <t>07.07.2026</t>
         </is>
       </c>
     </row>
@@ -6928,22 +6854,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Щербаков Михаил · Вековищев Григорий · Бабинич Егор · Черепков Андрей</t>
+          <t>Торопкин Богдан · Щербаков Михаил · Вишняков Савелий · Вековищев Григорий</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7:10.39</t>
+          <t>7:09.16</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>22.08.2025</t>
+          <t>11.07.2026</t>
         </is>
       </c>
     </row>
@@ -7796,22 +7722,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Щербаков Михаил · Жидков Роман · Полещук Мария · Манохина Кира</t>
+          <t>Прошин Егор · Щербаков Михаил · Сорокина Ксения · Манохина Кира</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3:26.93</t>
+          <t>3:23.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Отопени</t>
+          <t>Мюнхен</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.08.2025</t>
+          <t>08.07.2026</t>
         </is>
       </c>
     </row>

--- a/public/records.xlsx
+++ b/public/records.xlsx
@@ -863,27 +863,27 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54.07</t>
+          <t>54.06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54.07</t>
+          <t>54.06</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Мюнхен</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -1055,27 +1055,27 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1:58.06</t>
+          <t>1:57.10</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>118.06</t>
+          <t>117.10</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>19.04.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -3199,27 +3199,27 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1:57.07</t>
+          <t>1:56.16</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>117.07</t>
+          <t>116.16</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Мюнхен</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>16.08.2026</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5167,17 +5167,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54.07</t>
+          <t>54.06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Мюнхен</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
     </row>
@@ -5279,17 +5279,17 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1:58.06</t>
+          <t>1:57.10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>19.04.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
     </row>
@@ -6651,17 +6651,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1:57.07</t>
+          <t>1:56.16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Мюнхен</t>
+          <t>Париж</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>16.08.2026</t>
         </is>
       </c>
     </row>
